--- a/Relatorio_Comissao.xlsx
+++ b/Relatorio_Comissao.xlsx
@@ -1361,18 +1361,42 @@
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="B22" t="n">
+        <v>482.25</v>
+      </c>
+      <c r="C22" t="n">
+        <v>9</v>
+      </c>
+      <c r="D22" t="n">
+        <v>42.87</v>
+      </c>
+      <c r="E22" t="n">
+        <v>42.87</v>
+      </c>
+      <c r="F22" t="n">
+        <v>42.87</v>
+      </c>
+      <c r="G22" t="n">
+        <v>42.87</v>
+      </c>
+      <c r="H22" t="n">
+        <v>42.87</v>
+      </c>
+      <c r="I22" t="n">
+        <v>42.87</v>
+      </c>
+      <c r="J22" t="n">
+        <v>42.87</v>
+      </c>
+      <c r="K22" t="n">
+        <v>42.87</v>
+      </c>
+      <c r="L22" t="n">
+        <v>42.87</v>
+      </c>
+      <c r="M22" t="n">
+        <v>42.87</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1380,18 +1404,42 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="B23" t="n">
+        <v>291.8</v>
+      </c>
+      <c r="C23" t="n">
+        <v>9</v>
+      </c>
+      <c r="D23" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="E23" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="F23" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="G23" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="H23" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="I23" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="J23" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="K23" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="L23" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="M23" t="n">
+        <v>25.94</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1399,18 +1447,42 @@
           <t>2026-02-23</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>171.65</v>
+      </c>
+      <c r="C24" t="n">
+        <v>9</v>
+      </c>
+      <c r="D24" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="E24" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="F24" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="G24" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="H24" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="I24" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="J24" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="K24" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="L24" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="M24" t="n">
+        <v>15.26</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1426,7 +1498,9 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
@@ -1445,7 +1519,9 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
@@ -1464,7 +1540,9 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
@@ -1483,7 +1561,9 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>

--- a/Relatorio_Comissao.xlsx
+++ b/Relatorio_Comissao.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1490,20 +1490,42 @@
           <t>2026-02-24</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="B25" t="n">
+        <v>257.8</v>
+      </c>
+      <c r="C25" t="n">
+        <v>8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="E25" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="F25" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="G25" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="H25" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="I25" t="n">
+        <v>25.78</v>
+      </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="L25" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="M25" t="n">
+        <v>25.78</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1511,20 +1533,42 @@
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="B26" t="n">
+        <v>224.85</v>
+      </c>
+      <c r="C26" t="n">
+        <v>8</v>
+      </c>
+      <c r="D26" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="E26" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="F26" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="G26" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="H26" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="I26" t="n">
+        <v>22.48</v>
+      </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="K26" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="L26" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="M26" t="n">
+        <v>22.48</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1532,20 +1576,42 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+      <c r="B27" t="n">
+        <v>221.6</v>
+      </c>
+      <c r="C27" t="n">
+        <v>8</v>
+      </c>
+      <c r="D27" t="n">
+        <v>22.16</v>
+      </c>
+      <c r="E27" t="n">
+        <v>22.16</v>
+      </c>
+      <c r="F27" t="n">
+        <v>22.16</v>
+      </c>
+      <c r="G27" t="n">
+        <v>22.16</v>
+      </c>
+      <c r="H27" t="n">
+        <v>22.16</v>
+      </c>
+      <c r="I27" t="n">
+        <v>22.16</v>
+      </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="K27" t="n">
+        <v>22.16</v>
+      </c>
+      <c r="L27" t="n">
+        <v>22.16</v>
+      </c>
+      <c r="M27" t="n">
+        <v>22.16</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1553,20 +1619,42 @@
           <t>2026-02-27</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="B28" t="n">
+        <v>256.9</v>
+      </c>
+      <c r="C28" t="n">
+        <v>8</v>
+      </c>
+      <c r="D28" t="n">
+        <v>25.69</v>
+      </c>
+      <c r="E28" t="n">
+        <v>25.69</v>
+      </c>
+      <c r="F28" t="n">
+        <v>25.69</v>
+      </c>
+      <c r="G28" t="n">
+        <v>25.69</v>
+      </c>
+      <c r="H28" t="n">
+        <v>25.69</v>
+      </c>
+      <c r="I28" t="n">
+        <v>25.69</v>
+      </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="K28" t="n">
+        <v>25.69</v>
+      </c>
+      <c r="L28" t="n">
+        <v>25.69</v>
+      </c>
+      <c r="M28" t="n">
+        <v>25.69</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1574,18 +1662,655 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="B29" t="n">
+        <v>368.5</v>
+      </c>
+      <c r="C29" t="n">
+        <v>9</v>
+      </c>
+      <c r="D29" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="E29" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="F29" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="G29" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="H29" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="I29" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="J29" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="K29" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="L29" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="M29" t="n">
+        <v>32.76</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>323.55</v>
+      </c>
+      <c r="C30" t="n">
+        <v>8</v>
+      </c>
+      <c r="D30" t="n">
+        <v>32.36</v>
+      </c>
+      <c r="E30" t="n">
+        <v>32.36</v>
+      </c>
+      <c r="F30" t="n">
+        <v>32.36</v>
+      </c>
+      <c r="G30" t="n">
+        <v>32.36</v>
+      </c>
+      <c r="H30" t="n">
+        <v>32.36</v>
+      </c>
+      <c r="I30" t="n">
+        <v>32.36</v>
+      </c>
+      <c r="J30" t="n">
+        <v>32.36</v>
+      </c>
+      <c r="K30" t="n">
+        <v>32.36</v>
+      </c>
+      <c r="L30" t="n">
+        <v>32.36</v>
+      </c>
+      <c r="M30" t="n">
+        <v>32.36</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Relatorio_Comissao.xlsx
+++ b/Relatorio_Comissao.xlsx
@@ -570,18 +570,42 @@
       <c r="A3" s="2" t="n">
         <v>46083</v>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>153.5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D3" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="E3" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="F3" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="G3" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="H3" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="I3" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="J3" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="K3" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="L3" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="M3" t="n">
+        <v>13.64</v>
+      </c>
       <c r="N3" t="n">
         <v>2026</v>
       </c>
@@ -598,18 +622,42 @@
       <c r="A4" s="2" t="n">
         <v>46084</v>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>281.9</v>
+      </c>
+      <c r="C4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="E4" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="F4" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="G4" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="H4" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="I4" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="J4" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="K4" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="L4" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="M4" t="n">
+        <v>25.06</v>
+      </c>
       <c r="N4" t="n">
         <v>2026</v>
       </c>

--- a/Relatorio_Comissao.xlsx
+++ b/Relatorio_Comissao.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,38 +675,75 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>16.096</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>16.096</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>16.096</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>16.096</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>16.096</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>16.096</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>16.096</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>16.096</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>16.096</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>16.096</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>92.10799999999999</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>92.10799999999999</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>92.10799999999999</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>92.10799999999999</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>92.10799999999999</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>92.10799999999999</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>92.10799999999999</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>92.10799999999999</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>92.10799999999999</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>92.10799999999999</v>
+      <c r="B8" s="3" t="n">
+        <v>108.204</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>108.204</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>108.204</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>108.204</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>108.204</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>108.204</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>108.204</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>108.204</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>108.204</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>108.204</v>
       </c>
     </row>
   </sheetData>

--- a/Relatorio_Comissao.xlsx
+++ b/Relatorio_Comissao.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -712,38 +712,75 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>27.944</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>27.944</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>27.944</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>27.944</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>27.944</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>27.944</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>27.944</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>27.944</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>27.944</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>27.944</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>108.204</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>108.204</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>108.204</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>108.204</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>108.204</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>108.204</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>108.204</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>108.204</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>108.204</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>108.204</v>
+      <c r="B9" s="3" t="n">
+        <v>136.148</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>136.148</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>136.148</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>136.148</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>136.148</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>136.148</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>136.148</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>136.148</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>136.148</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>136.148</v>
       </c>
     </row>
   </sheetData>

--- a/Relatorio_Comissao.xlsx
+++ b/Relatorio_Comissao.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -749,38 +749,75 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>28.064</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>28.064</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>28.064</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>28.064</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>28.064</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>28.064</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>28.064</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>28.064</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>28.064</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>28.064</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>136.148</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>136.148</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>136.148</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>136.148</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>136.148</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>136.148</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>136.148</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>136.148</v>
-      </c>
-      <c r="J9" s="3" t="n">
-        <v>136.148</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>136.148</v>
+      <c r="B10" s="3" t="n">
+        <v>164.212</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>164.212</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>164.212</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>164.212</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>164.212</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>164.212</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>164.212</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>164.212</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>164.212</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>164.212</v>
       </c>
     </row>
   </sheetData>

--- a/Relatorio_Comissao.xlsx
+++ b/Relatorio_Comissao.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,38 +786,112 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>15.356</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>15.356</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>15.356</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>15.356</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>15.356</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>15.356</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>15.356</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>15.356</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>15.356</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>15.356</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>17.304</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>17.304</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>17.304</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>17.304</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>17.304</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>17.304</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>17.304</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>17.304</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>17.304</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>17.304</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>164.212</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>164.212</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>164.212</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>164.212</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>164.212</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>164.212</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>164.212</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>164.212</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>164.212</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>164.212</v>
+      <c r="B12" s="3" t="n">
+        <v>196.872</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>196.872</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>196.872</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>196.872</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>196.872</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>196.872</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>196.872</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>196.872</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>196.872</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>196.872</v>
       </c>
     </row>
   </sheetData>

--- a/Relatorio_Comissao.xlsx
+++ b/Relatorio_Comissao.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,38 +860,112 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>34.98800000000001</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>34.98800000000001</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>34.98800000000001</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>34.98800000000001</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>34.98800000000001</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>34.98800000000001</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>34.98800000000001</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>34.98800000000001</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>34.98800000000001</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>34.98800000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>17.868</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>17.868</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>17.868</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>17.868</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>17.868</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>17.868</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>17.868</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>17.868</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>17.868</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>17.868</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>196.872</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>196.872</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>196.872</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>196.872</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>196.872</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>196.872</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>196.872</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>196.872</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>196.872</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>196.872</v>
+      <c r="B14" s="3" t="n">
+        <v>249.728</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>249.728</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>249.728</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>249.728</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>249.728</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>249.728</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>249.728</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>249.728</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>249.728</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>249.728</v>
       </c>
     </row>
   </sheetData>

--- a/Relatorio_Comissao.xlsx
+++ b/Relatorio_Comissao.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -934,38 +934,75 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>14.196</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>14.196</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>14.196</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>14.196</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>14.196</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>14.196</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>14.196</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>14.196</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>14.196</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>14.196</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
-        <v>249.728</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>249.728</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>249.728</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>249.728</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>249.728</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>249.728</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>249.728</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>249.728</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>249.728</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>249.728</v>
+      <c r="B15" s="3" t="n">
+        <v>263.924</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>263.924</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>263.924</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>263.924</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>263.924</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>263.924</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>263.924</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>263.924</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>263.924</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>263.924</v>
       </c>
     </row>
   </sheetData>

--- a/Relatorio_Comissao.xlsx
+++ b/Relatorio_Comissao.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -971,38 +971,112 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>21.14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>18.856</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>18.856</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>18.856</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>18.856</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>18.856</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>18.856</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>18.856</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>18.856</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>18.856</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>18.856</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
-        <v>263.924</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>263.924</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>263.924</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>263.924</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>263.924</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>263.924</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>263.924</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>263.924</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>263.924</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>263.924</v>
+      <c r="B17" s="3" t="n">
+        <v>303.92</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>303.92</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>303.92</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>303.92</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>303.92</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>303.92</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>303.92</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>303.92</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>303.92</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>303.92</v>
       </c>
     </row>
   </sheetData>

--- a/Relatorio_Comissao.xlsx
+++ b/Relatorio_Comissao.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,38 +1045,112 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>12.524</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>12.524</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>12.524</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>12.524</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>12.524</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>12.524</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>12.524</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>12.524</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>12.524</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>12.524</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>15.36</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
-        <v>303.92</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>303.92</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>303.92</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>303.92</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>303.92</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>303.92</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>303.92</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>303.92</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>303.92</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>303.92</v>
+      <c r="B19" s="3" t="n">
+        <v>331.804</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>331.804</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>331.804</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>331.804</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>331.804</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>331.804</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>331.804</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>331.804</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>331.804</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>331.804</v>
       </c>
     </row>
   </sheetData>

--- a/Relatorio_Comissao.xlsx
+++ b/Relatorio_Comissao.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1119,38 +1119,75 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>9.087999999999999</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>9.087999999999999</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>9.087999999999999</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>9.087999999999999</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>9.087999999999999</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>9.087999999999999</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>9.087999999999999</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>9.087999999999999</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>9.087999999999999</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>9.087999999999999</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
-        <v>331.804</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>331.804</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>331.804</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>331.804</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>331.804</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>331.804</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>331.804</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>331.804</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>331.804</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>331.804</v>
+      <c r="B20" s="3" t="n">
+        <v>340.8920000000001</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>340.8920000000001</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>340.8920000000001</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>340.8920000000001</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>340.8920000000001</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>340.8920000000001</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>340.8920000000001</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>340.8920000000001</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>340.8920000000001</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>340.8920000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Relatorio_Comissao.xlsx
+++ b/Relatorio_Comissao.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1156,38 +1156,75 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>14.936</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>14.936</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>14.936</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>14.936</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>14.936</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>14.936</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>14.936</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>14.936</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>14.936</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>14.936</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>340.8920000000001</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>340.8920000000001</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>340.8920000000001</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>340.8920000000001</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>340.8920000000001</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>340.8920000000001</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>340.8920000000001</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>340.8920000000001</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>340.8920000000001</v>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>340.8920000000001</v>
+      <c r="B21" s="3" t="n">
+        <v>355.828</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>355.828</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>355.828</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>355.828</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>355.828</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>355.828</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>355.828</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>355.828</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>355.828</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>355.828</v>
       </c>
     </row>
   </sheetData>

--- a/Relatorio_Comissao.xlsx
+++ b/Relatorio_Comissao.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1193,38 +1193,75 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>20.076</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>20.076</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>20.076</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>20.076</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>20.076</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>20.076</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>20.076</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>20.076</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>20.076</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>20.076</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
-        <v>355.828</v>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>355.828</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>355.828</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>355.828</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>355.828</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>355.828</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>355.828</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>355.828</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>355.828</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>355.828</v>
+      <c r="B22" s="3" t="n">
+        <v>375.9040000000001</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>375.9040000000001</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>375.9040000000001</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>375.9040000000001</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>375.9040000000001</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>375.9040000000001</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>375.9040000000001</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>375.9040000000001</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>375.9040000000001</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>375.9040000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Relatorio_Comissao.xlsx
+++ b/Relatorio_Comissao.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1230,38 +1230,75 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
-        <v>375.9040000000001</v>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>375.9040000000001</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>375.9040000000001</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>375.9040000000001</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>375.9040000000001</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>375.9040000000001</v>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>375.9040000000001</v>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>375.9040000000001</v>
-      </c>
-      <c r="J22" s="3" t="n">
-        <v>375.9040000000001</v>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v>375.9040000000001</v>
+      <c r="B23" s="3" t="n">
+        <v>400.2040000000001</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>400.2040000000001</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>400.2040000000001</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>400.2040000000001</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>400.2040000000001</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>400.2040000000001</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>400.2040000000001</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>400.2040000000001</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>400.2040000000001</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>400.2040000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Relatorio_Comissao.xlsx
+++ b/Relatorio_Comissao.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1267,38 +1267,186 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>24.336</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>24.336</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>24.336</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>24.336</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>24.336</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>24.336</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>24.336</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>24.336</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>24.336</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>24.336</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>7.716000000000001</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>7.716000000000001</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>7.716000000000001</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>7.716000000000001</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>7.716000000000001</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>7.716000000000001</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>7.716000000000001</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>7.716000000000001</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>7.716000000000001</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>7.716000000000001</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>17.268</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>17.268</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>17.268</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>17.268</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>17.268</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>17.268</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>17.268</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>17.268</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>17.268</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>17.268</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>16.652</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>16.652</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>16.652</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>16.652</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>16.652</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>16.652</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>16.652</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>16.652</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>16.652</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>16.652</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
-        <v>400.2040000000001</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>400.2040000000001</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>400.2040000000001</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>400.2040000000001</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>400.2040000000001</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>400.2040000000001</v>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>400.2040000000001</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>400.2040000000001</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>400.2040000000001</v>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>400.2040000000001</v>
+      <c r="B27" s="3" t="n">
+        <v>466.176</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>466.176</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>466.176</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>466.176</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>466.176</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>466.176</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>466.176</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>466.176</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>466.176</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>466.176</v>
       </c>
     </row>
   </sheetData>

--- a/Relatorio_Comissao.xlsx
+++ b/Relatorio_Comissao.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1415,38 +1415,75 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>13.892</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>13.892</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>13.892</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>13.892</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>13.892</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>13.892</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>13.892</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>13.892</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>13.892</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>13.892</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n">
-        <v>466.176</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>466.176</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>466.176</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>466.176</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>466.176</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>466.176</v>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>466.176</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>466.176</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>466.176</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>466.176</v>
+      <c r="B28" s="3" t="n">
+        <v>480.068</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>480.068</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>480.068</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>480.068</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>480.068</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>480.068</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>480.068</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>480.068</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>480.068</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>480.068</v>
       </c>
     </row>
   </sheetData>

--- a/Relatorio_Comissao.xlsx
+++ b/Relatorio_Comissao.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1452,38 +1452,75 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>15.004</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>15.004</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>15.004</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>15.004</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>15.004</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>15.004</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>15.004</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>15.004</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>15.004</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>15.004</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n">
-        <v>480.068</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>480.068</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>480.068</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>480.068</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>480.068</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>480.068</v>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>480.068</v>
-      </c>
-      <c r="I28" s="3" t="n">
-        <v>480.068</v>
-      </c>
-      <c r="J28" s="3" t="n">
-        <v>480.068</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>480.068</v>
+      <c r="B29" s="3" t="n">
+        <v>495.072</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>495.072</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>495.072</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>495.072</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>495.072</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>495.072</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>495.072</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>495.072</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>495.072</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>495.072</v>
       </c>
     </row>
   </sheetData>

--- a/Relatorio_Comissao.xlsx
+++ b/Relatorio_Comissao.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1489,38 +1489,75 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>27.632</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>27.632</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>27.632</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>27.632</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>27.632</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>27.632</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>27.632</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>27.632</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>27.632</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>27.632</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n">
-        <v>495.072</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>495.072</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>495.072</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>495.072</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>495.072</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>495.072</v>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>495.072</v>
-      </c>
-      <c r="I29" s="3" t="n">
-        <v>495.072</v>
-      </c>
-      <c r="J29" s="3" t="n">
-        <v>495.072</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>495.072</v>
+      <c r="B30" s="3" t="n">
+        <v>522.704</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>522.704</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>522.704</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>522.704</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>522.704</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>522.704</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>522.704</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>522.704</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>522.704</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>522.704</v>
       </c>
     </row>
   </sheetData>

--- a/Relatorio_Comissao.xlsx
+++ b/Relatorio_Comissao.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1526,38 +1526,149 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>33.312</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>33.312</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>33.312</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>33.312</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>33.312</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>33.312</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>33.312</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>33.312</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>33.312</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>33.312</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>17.34</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>16.696</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>16.696</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>16.696</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>16.696</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>16.696</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>16.696</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>16.696</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>16.696</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>16.696</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>16.696</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n">
-        <v>522.704</v>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>522.704</v>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>522.704</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>522.704</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>522.704</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>522.704</v>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>522.704</v>
-      </c>
-      <c r="I30" s="3" t="n">
-        <v>522.704</v>
-      </c>
-      <c r="J30" s="3" t="n">
-        <v>522.704</v>
-      </c>
-      <c r="K30" s="3" t="n">
-        <v>522.704</v>
+      <c r="B33" s="3" t="n">
+        <v>590.052</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>590.052</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>590.052</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>590.052</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>590.052</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>590.052</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>590.052</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>590.052</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>590.052</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>590.052</v>
       </c>
     </row>
   </sheetData>
